--- a/BROMappings/Mapping en definitie BRO GMW.xlsx
+++ b/BROMappings/Mapping en definitie BRO GMW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/Meny_OS/trunk/BronDatamodel/BROMappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{C98B97DB-AF31-43E8-BA33-4B0785DBF11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A34A134C-CEDE-4BA5-A343-64228824AF03}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{C98B97DB-AF31-43E8-BA33-4B0785DBF11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E8A8CA-489A-4909-9541-B4134B3CD64D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="332">
   <si>
     <t>Registratieobject</t>
   </si>
@@ -993,9 +993,6 @@
     <t>GLDID</t>
   </si>
   <si>
-    <t>sedSumpLength</t>
-  </si>
-  <si>
     <t>[IDCategorical]</t>
   </si>
   <si>
@@ -1021,6 +1018,12 @@
   </si>
   <si>
     <t>[mm]</t>
+  </si>
+  <si>
+    <t>BRO-ID</t>
+  </si>
+  <si>
+    <t>SedSumpLength</t>
   </si>
 </sst>
 </file>
@@ -1188,30 +1191,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person0.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person1.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person2.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person3.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person4.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1780,7 +1759,7 @@
         <v>271</v>
       </c>
       <c r="F6" t="s">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="G6" t="s">
         <v>70</v>
@@ -1989,7 +1968,7 @@
         <v>166</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>224</v>
@@ -2016,13 +1995,13 @@
         <v>141</v>
       </c>
       <c r="R10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -2043,7 +2022,7 @@
         <v>219</v>
       </c>
       <c r="G11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H11" t="s">
         <v>220</v>
@@ -2203,7 +2182,7 @@
         <v>227</v>
       </c>
       <c r="G14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H14" t="s">
         <v>220</v>
@@ -2257,7 +2236,7 @@
         <v>230</v>
       </c>
       <c r="G15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H15" t="s">
         <v>220</v>
@@ -2359,7 +2338,7 @@
         <v>236</v>
       </c>
       <c r="G17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H17" t="s">
         <v>220</v>
@@ -2461,7 +2440,7 @@
         <v>242</v>
       </c>
       <c r="G19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H19" t="s">
         <v>220</v>
@@ -2566,7 +2545,7 @@
         <v>248</v>
       </c>
       <c r="G21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H21" t="s">
         <v>220</v>
@@ -2667,7 +2646,7 @@
         <v>254</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>220</v>
@@ -2718,7 +2697,7 @@
         <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J24" s="6">
         <v>1</v>
@@ -3107,7 +3086,7 @@
         <v>46</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -3207,7 +3186,7 @@
         <v>171</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -3355,7 +3334,7 @@
         <v>177</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -3405,7 +3384,7 @@
         <v>178</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -3503,7 +3482,7 @@
         <v>180</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -3838,7 +3817,7 @@
         <v>187</v>
       </c>
       <c r="G47" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J47" s="6">
         <v>1</v>
@@ -4028,7 +4007,7 @@
         <v>191</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -4075,7 +4054,7 @@
         <v>192</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -4175,7 +4154,7 @@
         <v>52</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -4225,7 +4204,7 @@
         <v>194</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -4275,7 +4254,7 @@
         <v>195</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -4378,7 +4357,7 @@
         <v>197</v>
       </c>
       <c r="G58" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -4477,7 +4456,7 @@
         <v>199</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -4578,7 +4557,7 @@
         <v>201</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -5055,13 +5034,13 @@
         <v>35</v>
       </c>
       <c r="E72" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F72" t="s">
         <v>57</v>
       </c>
       <c r="G72" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J72" s="6">
         <v>0</v>
@@ -5100,13 +5079,13 @@
         <v>35</v>
       </c>
       <c r="E73" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F73" t="s">
         <v>58</v>
       </c>
       <c r="G73" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J73" s="6">
         <v>0</v>
@@ -5217,10 +5196,10 @@
         <v>86</v>
       </c>
       <c r="P75" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="Q75" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="R75" s="1" t="s">
         <v>56</v>
